--- a/previews/receipt.xlsx
+++ b/previews/receipt.xlsx
@@ -102,7 +102,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>355600</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
